--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://withie-my.sharepoint.com/personal/nko910730_withie_co_kr/Documents/바탕 화면/위드인천/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="124" documentId="11_2B59D2BFD390DACE3C2912D04B9230B648BFFC41" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C55B5305-2451-4E48-BA94-0479F9558589}"/>
+  <xr:revisionPtr revIDLastSave="146" documentId="11_2B59D2BFD390DACE3C2912D04B9230B648BFFC41" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51DDEEAC-ECA9-449C-88C3-1102F68048DC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1155" yWindow="1065" windowWidth="19200" windowHeight="11205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
   <si>
     <t>Tag</t>
   </si>
@@ -123,18 +123,6 @@
     <t>W_WATER_POND_Level_Status</t>
   </si>
   <si>
-    <t>L/L</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>L</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>H</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>H/H</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -143,9 +131,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>H</t>
-  </si>
-  <si>
     <t>DCS name</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -161,13 +146,13 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>L</t>
-  </si>
-  <si>
     <t>Update Time</t>
   </si>
   <si>
     <t>B</t>
+  </si>
+  <si>
+    <t>H/H</t>
   </si>
 </sst>
 </file>
@@ -201,7 +186,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -209,7 +194,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -256,14 +241,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -576,6 +561,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="7"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -583,380 +569,379 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
+        <v>31</v>
+      </c>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="D2" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D3" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="7"/>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="D4" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="7"/>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3100</v>
+      </c>
+      <c r="D5" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2">
+        <v>8325</v>
+      </c>
+      <c r="D6" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D7" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="7"/>
+      <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="D8" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="7"/>
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="7"/>
+      <c r="B10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="D10" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="5"/>
+      <c r="B11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="D11" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1852</v>
+      </c>
+      <c r="D12" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+      <c r="B13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="2">
+        <v>54</v>
+      </c>
+      <c r="D13" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+      <c r="B14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="D14" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="2">
+        <v>56</v>
+      </c>
+      <c r="D15" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="2">
+        <v>29</v>
+      </c>
+      <c r="D16" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="3">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="D2" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="D3" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="C17" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="2">
+        <v>13.1</v>
+      </c>
+      <c r="D18" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="D4" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="3">
-        <v>3000</v>
-      </c>
-      <c r="D5" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E5" s="3"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="C19" s="3">
+        <v>7</v>
+      </c>
+      <c r="D19" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="4">
+        <v>7.1</v>
+      </c>
+      <c r="D21" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="D22" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="3">
-        <v>8325</v>
-      </c>
-      <c r="D6" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E6" s="3"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="D7" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E7" s="3"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="3">
-        <v>0.06</v>
-      </c>
-      <c r="D8" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="3">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="3">
-        <v>4.3</v>
-      </c>
-      <c r="D10" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="D11" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="3">
-        <v>1852</v>
-      </c>
-      <c r="D12" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="3">
-        <v>54</v>
-      </c>
-      <c r="D13" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="D14" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B15" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="3">
-        <v>56</v>
-      </c>
-      <c r="D15" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B16" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="3">
-        <v>29</v>
-      </c>
-      <c r="D16" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E16" s="3"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E17" s="3"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B18" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="3">
-        <v>0</v>
-      </c>
-      <c r="D18" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E18" s="3"/>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="4">
-        <v>7</v>
-      </c>
-      <c r="D19" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E19" s="3"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E20" s="3"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B21" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="5">
-        <v>7.1</v>
-      </c>
-      <c r="D21" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E21" s="3"/>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="5">
-        <v>7.5</v>
-      </c>
-      <c r="D22" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E22" s="3"/>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E23" s="3"/>
+      <c r="D23" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E23" s="2"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="4">
         <v>7.8</v>
       </c>
-      <c r="D24" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E24" s="3"/>
+      <c r="D24" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E24" s="2"/>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E25" s="3"/>
+      <c r="C25" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E25" s="2"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="3">
-        <v>68.2</v>
-      </c>
-      <c r="D26" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E26" s="3"/>
+      <c r="C26" s="2">
+        <v>45.3</v>
+      </c>
+      <c r="D26" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E26" s="2"/>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="3">
-        <v>68.3</v>
-      </c>
-      <c r="D27" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E27" s="3"/>
+      <c r="C27" s="2">
+        <v>45</v>
+      </c>
+      <c r="D27" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E27" s="2"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="3">
-        <v>6</v>
-      </c>
-      <c r="D28" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E28" s="3"/>
+      <c r="C28" s="2">
+        <v>20</v>
+      </c>
+      <c r="D28" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E28" s="2"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="3">
-        <v>15</v>
-      </c>
-      <c r="D29" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E29" s="3"/>
+      <c r="C29" s="2">
+        <v>25</v>
+      </c>
+      <c r="D29" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E29" s="2"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="3">
-        <v>20</v>
-      </c>
-      <c r="D30" s="7">
-        <v>46098.349305555559</v>
-      </c>
-      <c r="E30" s="3"/>
+      <c r="C30" s="2">
+        <v>95</v>
+      </c>
+      <c r="D30" s="6">
+        <v>46098.349305555559</v>
+      </c>
+      <c r="E30" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://withie-my.sharepoint.com/personal/nko910730_withie_co_kr/Documents/바탕 화면/위드인천/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="146" documentId="11_2B59D2BFD390DACE3C2912D04B9230B648BFFC41" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51DDEEAC-ECA9-449C-88C3-1102F68048DC}"/>
+  <xr:revisionPtr revIDLastSave="148" documentId="11_2B59D2BFD390DACE3C2912D04B9230B648BFFC41" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCBB638F-4CB8-4FF0-B780-11218B838F54}"/>
   <bookViews>
-    <workbookView xWindow="1155" yWindow="1065" windowWidth="19200" windowHeight="11205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-2630" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -888,7 +888,7 @@
         <v>21</v>
       </c>
       <c r="C26" s="2">
-        <v>45.3</v>
+        <v>67.628</v>
       </c>
       <c r="D26" s="6">
         <v>46098.349305555559</v>
@@ -900,7 +900,7 @@
         <v>22</v>
       </c>
       <c r="C27" s="2">
-        <v>45</v>
+        <v>67.605999999999995</v>
       </c>
       <c r="D27" s="6">
         <v>46098.349305555559</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://withie-my.sharepoint.com/personal/nko910730_withie_co_kr/Documents/바탕 화면/위드인천/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://withie-my.sharepoint.com/personal/nko910730_withie_co_kr/Documents/바탕 화면/위드인천/환경 통합 모니터링/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="148" documentId="11_2B59D2BFD390DACE3C2912D04B9230B648BFFC41" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCBB638F-4CB8-4FF0-B780-11218B838F54}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="11_2B59D2BFD390DACE3C2912D04B9230B648BFFC41" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10436A78-F68A-424A-8D5C-094940E137C4}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-2630" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Tag</t>
   </si>
@@ -733,7 +733,7 @@
         <v>13</v>
       </c>
       <c r="C13" s="2">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D13" s="6">
         <v>46098.349305555559</v>
@@ -758,7 +758,7 @@
         <v>15</v>
       </c>
       <c r="C15" s="2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D15" s="6">
         <v>46098.349305555559</v>
@@ -851,9 +851,7 @@
       <c r="B23" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="C23" s="4"/>
       <c r="D23" s="6">
         <v>46098.349305555559</v>
       </c>
@@ -888,7 +886,7 @@
         <v>21</v>
       </c>
       <c r="C26" s="2">
-        <v>67.628</v>
+        <v>67.62</v>
       </c>
       <c r="D26" s="6">
         <v>46098.349305555559</v>
@@ -900,7 +898,7 @@
         <v>22</v>
       </c>
       <c r="C27" s="2">
-        <v>67.605999999999995</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="D27" s="6">
         <v>46098.349305555559</v>
